--- a/laporan_padel_dki_jakarta_2026-10-11.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-11.xlsx
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp13.112.000</t>
+          <t>Rp13.442.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>36</v>
       </c>
       <c r="D54" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp200.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>72</v>
       </c>
       <c r="D62" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp2.142.000</t>
+          <t>Rp2.402.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp2.277.000</t>
+          <t>Rp2.376.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>96</v>
       </c>
       <c r="D70" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp3.860.000</t>
+          <t>Rp4.370.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp3.465.000</t>
+          <t>Rp3.663.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>34</v>
       </c>
       <c r="D94" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp375.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.187.000</t>
+          <t>Rp2.349.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.074.000</t>
+          <t>Rp2.199.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp21.800.000</t>
+          <t>Rp22.350.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.804.000</t>
+          <t>Rp6.895.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>48</v>
       </c>
       <c r="D24" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp899.000</t>
+          <t>Rp1.059.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp14.800.000</t>
+          <t>Rp14.900.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>170</v>
       </c>
       <c r="D40" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp22.249.000</t>
+          <t>Rp22.949.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-11.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-11.xlsx
@@ -947,16 +947,16 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp375.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.582.000</t>
+          <t>Rp4.346.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.935.000</t>
+          <t>Rp2.025.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>85</v>
       </c>
       <c r="D60" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp894.000</t>
+          <t>Rp1.043.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>68</v>
       </c>
       <c r="D71" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp240.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.690.000</t>
+          <t>Rp1.840.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>96</v>
       </c>
       <c r="D74" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp675.000</t>
+          <t>Rp540.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>98</v>
       </c>
       <c r="D75" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp3.950.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp13.735.000</t>
+          <t>Rp13.345.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>34</v>
       </c>
       <c r="D94" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>133</v>
       </c>
       <c r="D3" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp17.415.500</t>
+          <t>Rp17.767.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp7.450.000</t>
+          <t>Rp7.800.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.600.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.260.000</t>
+          <t>Rp3.325.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>176</v>
       </c>
       <c r="D37" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp9.750.000</t>
+          <t>Rp10.300.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp5.675.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5338,16 +5338,16 @@
         <v>124</v>
       </c>
       <c r="D59" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp760.000</t>
+          <t>Rp880.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp8.400.000</t>
+          <t>Rp9.000.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.775.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp8.000.000</t>
+          <t>Rp8.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp31.800.000</t>
+          <t>Rp32.500.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.547.000</t>
+          <t>Rp8.047.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.895.000</t>
+          <t>Rp7.057.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp14.900.000</t>
+          <t>Rp16.600.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>128</v>
       </c>
       <c r="D41" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.289.000</t>
+          <t>Rp3.887.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>102</v>
       </c>
       <c r="D49" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.650.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.190.000</t>
+          <t>Rp15.310.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp11.210.000</t>
+          <t>Rp10.510.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>68</v>
       </c>
       <c r="D23" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp675.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.799.981</t>
+          <t>Rp3.999.980</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>51</v>
       </c>
       <c r="D38" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.480.000</t>
+          <t>Rp1.665.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>72</v>
       </c>
       <c r="D39" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.970.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-11.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-11.xlsx
@@ -544,16 +544,16 @@
         <v>176</v>
       </c>
       <c r="D4" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp19.540.000</t>
+          <t>Rp20.940.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp264.000</t>
+          <t>Rp440.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp5.200.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.245.000</t>
+          <t>Rp3.295.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.937.000</t>
+          <t>Rp2.533.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp13.442.000</t>
+          <t>Rp13.909.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp15.580.000</t>
+          <t>Rp15.780.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.355.000</t>
+          <t>Rp2.415.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.080.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp13.235.000</t>
+          <t>Rp13.733.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.713.000</t>
+          <t>Rp1.812.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp560.000</t>
+          <t>Rp675.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>17</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp1.192.000</t>
+          <t>Rp1.341.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.925.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp2.385.000</t>
+          <t>Rp2.703.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>96</v>
       </c>
       <c r="D70" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp4.370.000</t>
+          <t>Rp4.520.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.840.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>98</v>
       </c>
       <c r="D75" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp4.350.000</t>
+          <t>Rp4.770.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp13.345.000</t>
+          <t>Rp13.540.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>114</v>
       </c>
       <c r="D79" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp2.975.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>96</v>
       </c>
       <c r="D85" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp3.675.000</t>
+          <t>Rp3.835.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>64</v>
       </c>
       <c r="D96" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp375.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp5.390.000</t>
+          <t>Rp5.590.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>133</v>
       </c>
       <c r="D3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp17.767.500</t>
+          <t>Rp17.943.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.199.000</t>
+          <t>Rp2.324.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.445.000</t>
+          <t>Rp7.825.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.985.000</t>
+          <t>Rp3.460.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp5.200.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>64</v>
       </c>
       <c r="D27" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.025.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>180</v>
       </c>
       <c r="D28" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp25.630.000</t>
+          <t>Rp26.365.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.175.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>176</v>
       </c>
       <c r="D37" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp10.300.000</t>
+          <t>Rp11.500.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp6.200.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>11</v>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp425.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp6.125.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>72</v>
       </c>
       <c r="D51" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp3.184.000</t>
+          <t>Rp3.582.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.250.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp9.240.000</t>
+          <t>Rp9.515.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp714.000</t>
+          <t>Rp1.047.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5338,16 +5338,16 @@
         <v>124</v>
       </c>
       <c r="D59" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp880.000</t>
+          <t>Rp1.120.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>36</v>
       </c>
       <c r="D62" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.490.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp3.775.000</t>
+          <t>Rp4.175.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp160.000</t>
+          <t>Rp320.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp8.500.000</t>
+          <t>Rp9.000.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp720.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp32.500.000</t>
+          <t>Rp33.200.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp6.350.000</t>
+          <t>Rp7.600.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp398.000</t>
+          <t>Rp1.194.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.024.000</t>
+          <t>Rp3.192.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp20.610.000</t>
+          <t>Rp18.810.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>82</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp13.675.000</t>
+          <t>Rp14.435.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp17.725.000</t>
+          <t>Rp18.115.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp14.535.000</t>
+          <t>Rp15.635.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.256.000</t>
+          <t>Rp2.068.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.825.000</t>
+          <t>Rp4.125.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>60</v>
       </c>
       <c r="D20" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.287.000</t>
+          <t>Rp1.386.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp19.400.000</t>
+          <t>Rp19.800.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.057.000</t>
+          <t>Rp7.624.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>48</v>
       </c>
       <c r="D24" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp1.059.000</t>
+          <t>Rp1.219.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp350.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>96</v>
       </c>
       <c r="D29" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.470.000</t>
+          <t>Rp3.870.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp5.943.000</t>
+          <t>Rp6.520.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>108</v>
       </c>
       <c r="D33" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp16.600.000</t>
+          <t>Rp17.850.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.632.000</t>
+          <t>Rp2.820.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>14</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.925.000</t>
+          <t>Rp2.275.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>170</v>
       </c>
       <c r="D40" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp22.949.000</t>
+          <t>Rp23.649.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>128</v>
       </c>
       <c r="D41" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.887.000</t>
+          <t>Rp4.485.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>102</v>
       </c>
       <c r="D49" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>144</v>
       </c>
       <c r="D50" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.425.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.265.000</t>
+          <t>Rp2.785.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp6.580.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.450.000</t>
+          <t>Rp6.900.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.965.000</t>
+          <t>Rp8.230.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.280.000</t>
+          <t>Rp2.660.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>54</v>
       </c>
       <c r="D28" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>32</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.550.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>72</v>
       </c>
       <c r="D39" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.970.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-11.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-11.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.540.000</t>
+          <t>Rp1.640.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.700.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.158.000</t>
+          <t>Rp4.752.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.425.000</t>
+          <t>Rp3.525.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp13.909.500</t>
+          <t>Rp14.770.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.600.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.130.000</t>
+          <t>Rp2.340.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp15.780.000</t>
+          <t>Rp16.480.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp13.749.000</t>
+          <t>Rp13.998.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp375.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.960.000</t>
+          <t>Rp4.059.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.415.000</t>
+          <t>Rp2.815.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.838.000</t>
+          <t>Rp2.580.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.720.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.285.000</t>
+          <t>Rp4.855.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.043.000</t>
+          <t>Rp3.222.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.147.000</t>
+          <t>Rp4.122.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp810.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp13.733.000</t>
+          <t>Rp14.331.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.812.000</t>
+          <t>Rp2.022.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.630.000</t>
+          <t>Rp1.830.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>48</v>
       </c>
       <c r="D56" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp1.020.000</t>
+          <t>Rp1.220.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>54</v>
       </c>
       <c r="D57" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp160.000</t>
+          <t>Rp240.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp2.925.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp2.703.000</t>
+          <t>Rp2.862.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>72</v>
       </c>
       <c r="D62" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp2.402.000</t>
+          <t>Rp2.642.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>32</v>
       </c>
       <c r="D67" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp2.376.000</t>
+          <t>Rp2.574.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>128</v>
       </c>
       <c r="D69" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp1.294.000</t>
+          <t>Rp1.493.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>96</v>
       </c>
       <c r="D70" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp4.520.000</t>
+          <t>Rp4.370.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>68</v>
       </c>
       <c r="D71" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp780.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>98</v>
       </c>
       <c r="D75" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp4.770.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>45</v>
       </c>
       <c r="D76" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp13.540.000</t>
+          <t>Rp13.785.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp3.663.000</t>
+          <t>Rp4.357.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>80</v>
       </c>
       <c r="D87" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp698.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp3.825.000</t>
+          <t>Rp4.225.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp3.835.000</t>
+          <t>Rp4.195.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp5.590.000</t>
+          <t>Rp6.560.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.349.000</t>
+          <t>Rp2.430.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>133</v>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp17.943.500</t>
+          <t>Rp18.471.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp6.224.000</t>
+          <t>Rp7.780.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp5.820.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.460.000</t>
+          <t>Rp4.160.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp6.700.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp780.000</t>
+          <t>Rp1.170.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>180</v>
       </c>
       <c r="D28" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp26.365.000</t>
+          <t>Rp26.355.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.325.000</t>
+          <t>Rp4.390.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp6.175.000</t>
+          <t>Rp6.550.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4966,16 +4966,16 @@
         <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp6.125.000</t>
+          <t>Rp6.475.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>72</v>
       </c>
       <c r="D51" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp3.582.000</t>
+          <t>Rp3.980.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp9.515.000</t>
+          <t>Rp10.065.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp1.047.000</t>
+          <t>Rp1.218.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>45</v>
       </c>
       <c r="D61" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp9.000.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp4.175.000</t>
+          <t>Rp4.375.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp5.005.000</t>
+          <t>Rp8.277.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.625.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.000.000</t>
+          <t>Rp10.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp33.200.000</t>
+          <t>Rp34.400.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp465.000</t>
+          <t>Rp534.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp18.115.000</t>
+          <t>Rp18.475.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.475.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.047.000</t>
+          <t>Rp8.297.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.068.000</t>
+          <t>Rp3.196.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp22.350.000</t>
+          <t>Rp23.825.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6835,21 +6835,21 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp250.000</t>
+          <t>Rp50.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -6866,16 +6866,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.125.000</t>
+          <t>Rp4.425.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp19.800.000</t>
+          <t>Rp20.900.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.890.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>96</v>
       </c>
       <c r="D29" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.870.000</t>
+          <t>Rp6.590.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp6.520.000</t>
+          <t>Rp7.770.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>108</v>
       </c>
       <c r="D33" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp17.850.000</t>
+          <t>Rp18.850.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.820.000</t>
+          <t>Rp2.632.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>108</v>
       </c>
       <c r="D36" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.192.000</t>
+          <t>Rp1.788.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>128</v>
       </c>
       <c r="D41" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp4.485.000</t>
+          <t>Rp4.784.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>102</v>
       </c>
       <c r="D46" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp550.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>36</v>
       </c>
       <c r="D47" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp7.400.000</t>
+          <t>Rp7.800.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>102</v>
       </c>
       <c r="D49" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>144</v>
       </c>
       <c r="D50" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp2.425.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.785.000</t>
+          <t>Rp3.045.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.900.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp8.230.000</t>
+          <t>Rp10.030.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.799.976</t>
+          <t>Rp5.199.974</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.155.000</t>
+          <t>Rp1.270.500</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.660.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp7.560.000</t>
+          <t>Rp7.770.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.999.980</t>
+          <t>Rp4.199.979</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>54</v>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp6.600.000</t>
+          <t>Rp7.050.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp350.000</t>
+          <t>Rp525.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>54</v>
       </c>
       <c r="D33" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.390.000</t>
+          <t>Rp3.635.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>34</v>
       </c>
       <c r="D34" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.390.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>51</v>
       </c>
       <c r="D38" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.665.000</t>
+          <t>Rp2.220.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>72</v>
       </c>
       <c r="D39" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>72</v>
       </c>
       <c r="D42" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp540.000</t>
+          <t>Rp720.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>68</v>
       </c>
       <c r="D43" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp720.000</t>
+          <t>Rp1.440.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-11.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-11.xlsx
@@ -544,16 +544,16 @@
         <v>176</v>
       </c>
       <c r="D4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp20.940.000</t>
+          <t>Rp21.190.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.340.000</t>
+          <t>Rp2.440.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.350.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp1.875.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>90</v>
       </c>
       <c r="D89" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp2.880.000</t>
+          <t>Rp3.120.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5338,16 +5338,16 @@
         <v>124</v>
       </c>
       <c r="D59" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.120.000</t>
+          <t>Rp1.360.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>88</v>
       </c>
       <c r="D67" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp6.670.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5710,16 +5710,16 @@
         <v>90</v>
       </c>
       <c r="D71" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp4.725.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp18.810.000</t>
+          <t>Rp19.210.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>106</v>
       </c>
       <c r="D3" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp7.910.000</t>
+          <t>Rp8.410.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp534.000</t>
+          <t>Rp870.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp18.475.000</t>
+          <t>Rp18.670.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp15.635.000</t>
+          <t>Rp15.805.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.900.000</t>
+          <t>Rp21.100.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.624.000</t>
+          <t>Rp7.705.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.375.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp18.850.000</t>
+          <t>Rp19.125.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>128</v>
       </c>
       <c r="D41" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp4.784.000</t>
+          <t>Rp5.083.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>80</v>
       </c>
       <c r="D42" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.375.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.470.000</t>
+          <t>Rp2.620.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.600.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
